--- a/策划/excel/21_BattleEffect.xlsx
+++ b/策划/excel/21_BattleEffect.xlsx
@@ -12,27 +12,192 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="200" formatCode="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" ns1:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="0"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="24">
     <font>
       <sz val="11"/>
-      <name val="Carlito"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Microsoft YaHei"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -41,16 +206,192 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE7EDF3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34495E"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -58,65 +399,341 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <extLst>
-        <ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <extLst>
-        <ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-      <extLst>
-        <ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-      <extLst>
-        <ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </ext>
-      </extLst>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns2:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -332,56 +949,56 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.571428298950195" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="27.14285659790039" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="22.85714340209961" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="17.85714340209961" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="55.71428680419922" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="15" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="51.42856979370117" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="81.42857360839844" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="16.428571701049805" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="14.285714149475098" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="14.285714149475098" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="15.752380952381" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="13.247619047619" customWidth="1"/>
+    <col min="4" max="4" width="13.247619047619" customWidth="1"/>
+    <col min="5" max="5" width="165.857142857143" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="83.8571428571429" customWidth="1"/>
+    <col min="8" max="8" width="83.8571428571429" customWidth="1"/>
+    <col min="9" max="9" width="13.247619047619" customWidth="1"/>
+    <col min="10" max="10" width="14.2857142857143" customWidth="1"/>
+    <col min="11" max="11" width="14.2857142857143" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="10" t="str">
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="7" t="str">
         <v>编号【KEY】</v>
       </c>
-      <c r="B1" s="10" t="str">
+      <c r="B1" s="8" t="str">
         <v>效果枚举</v>
       </c>
-      <c r="C1" s="10" t="str">
+      <c r="C1" s="8" t="str">
         <v>效果名称</v>
       </c>
-      <c r="D1" s="10" t="str">
+      <c r="D1" s="8" t="str">
         <v>效果分类</v>
       </c>
-      <c r="E1" s="10" t="str">
+      <c r="E1" s="8" t="str">
         <v>效果说明</v>
       </c>
-      <c r="F1" s="10" t="str">
+      <c r="F1" s="8" t="str">
         <v>默认目标</v>
       </c>
-      <c r="G1" s="10" t="str">
+      <c r="G1" s="8" t="str">
         <v>默认参数</v>
       </c>
-      <c r="H1" s="10" t="str">
+      <c r="H1" s="8" t="str">
         <v>参数编辑字段</v>
       </c>
-      <c r="I1" s="10" t="str">
+      <c r="I1" s="8" t="str">
         <v>子效果容器</v>
       </c>
-      <c r="J1" s="10" t="str">
+      <c r="J1" s="8" t="str">
         <v>卡牌可用</v>
       </c>
-      <c r="K1" s="10" t="str">
+      <c r="K1" s="8" t="str">
         <v>敌人可用</v>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="8" t="str">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="str">
         <v>id</v>
       </c>
       <c r="B2" s="8" t="str">
@@ -415,8 +1032,8 @@
         <v>enemyEnabled</v>
       </c>
     </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="8" t="str">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="7" t="str">
         <v>int</v>
       </c>
       <c r="B3" s="8" t="str">
@@ -450,8 +1067,8 @@
         <v>boolean</v>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="8" t="str">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="7" t="str">
         <v>server</v>
       </c>
       <c r="B4" s="8" t="str">
@@ -485,8 +1102,8 @@
         <v>server</v>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="8" t="str">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="7" t="str">
         <v>client</v>
       </c>
       <c r="B5" s="8" t="str">
@@ -520,1337 +1137,1337 @@
         <v>client</v>
       </c>
     </row>
-    <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="11" t="n">
+    <row r="6" ht="70.0" customHeight="1">
+      <c r="A6" s="9" t="n">
         <v>210001</v>
       </c>
-      <c r="B6" s="6" t="str">
+      <c r="B6" s="10" t="str">
         <v>DAMAGE</v>
       </c>
-      <c r="C6" s="6" t="str">
+      <c r="C6" s="10" t="str">
         <v>造成伤害</v>
       </c>
-      <c r="D6" s="6" t="str">
+      <c r="D6" s="10" t="str">
         <v>基础战斗</v>
       </c>
-      <c r="E6" s="6" t="str">
+      <c r="E6" s="11" t="str">
         <v>普通 / 穿透 / 生命损失 / 多段 / 动态伤害</v>
       </c>
-      <c r="F6" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G6" s="6" t="str">
+      <c r="F6" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G6" s="11" t="str">
         <v>{"amount":6,"hits":1,"damageKind":"ATTACK","ignoreBlock":false}</v>
       </c>
-      <c r="H6" s="6" t="str">
+      <c r="H6" s="11" t="str">
         <v>[{"key":"amount","label":"单次基础伤害","kind":"expr","options":null},{"key":"hits","label":"攻击次数","kind":"expr","options":null},{"key":"damageKind","label":"伤害类型","kind":"enum","options":["ATTACK","THORNS","HP_LOSS","SPECIAL"]},{"key":"ignoreBlock","label":"无视格挡","kind":"bool","options":null}]</v>
       </c>
-      <c r="I6" s="6" t="str"/>
-      <c r="J6" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" ht="90" customHeight="1">
-      <c r="A7" s="11" t="n">
+      <c r="I6" s="10" t="str"/>
+      <c r="J6" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="37.0" customHeight="1">
+      <c r="A7" s="9" t="n">
         <v>210002</v>
       </c>
-      <c r="B7" s="6" t="str">
+      <c r="B7" s="10" t="str">
         <v>BLOCK</v>
       </c>
-      <c r="C7" s="6" t="str">
+      <c r="C7" s="10" t="str">
         <v>获得格挡</v>
       </c>
-      <c r="D7" s="6" t="str">
+      <c r="D7" s="10" t="str">
         <v>基础战斗</v>
       </c>
-      <c r="E7" s="6" t="str">
+      <c r="E7" s="11" t="str">
         <v>可以使用动态表达式</v>
       </c>
-      <c r="F7" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G7" s="6" t="str">
+      <c r="F7" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G7" s="11" t="str">
         <v>{"amount":5,"scale":true}</v>
       </c>
-      <c r="H7" s="6" t="str">
+      <c r="H7" s="11" t="str">
         <v>[{"key":"amount","label":"格挡值","kind":"expr","options":null},{"key":"scale","label":"敏捷和脆弱影响格挡","kind":"bool","options":null}]</v>
       </c>
-      <c r="I7" s="6" t="str"/>
-      <c r="J7" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
-      <c r="A8" s="11" t="n">
+      <c r="I7" s="10" t="str"/>
+      <c r="J7" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="9" t="n">
         <v>210003</v>
       </c>
-      <c r="B8" s="6" t="str">
+      <c r="B8" s="10" t="str">
         <v>HEAL</v>
       </c>
-      <c r="C8" s="6" t="str">
+      <c r="C8" s="10" t="str">
         <v>回复生命</v>
       </c>
-      <c r="D8" s="6" t="str">
+      <c r="D8" s="10" t="str">
         <v>基础战斗</v>
       </c>
-      <c r="E8" s="6" t="str">
+      <c r="E8" s="11" t="str">
         <v>可使用 @last_damage.total_hp_loss</v>
       </c>
-      <c r="F8" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G8" s="6" t="str">
+      <c r="F8" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G8" s="11" t="str">
         <v>{"amount":4}</v>
       </c>
-      <c r="H8" s="6" t="str">
+      <c r="H8" s="11" t="str">
         <v>[{"key":"amount","label":"回复量","kind":"expr","options":null}]</v>
       </c>
-      <c r="I8" s="6" t="str"/>
-      <c r="J8" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="90" customHeight="1">
-      <c r="A9" s="11" t="n">
+      <c r="I8" s="10" t="str"/>
+      <c r="J8" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="37.0" customHeight="1">
+      <c r="A9" s="9" t="n">
         <v>210004</v>
       </c>
-      <c r="B9" s="6" t="str">
+      <c r="B9" s="10" t="str">
         <v>LOSE_HP</v>
       </c>
-      <c r="C9" s="6" t="str">
+      <c r="C9" s="10" t="str">
         <v>直接失去生命</v>
       </c>
-      <c r="D9" s="6" t="str">
+      <c r="D9" s="10" t="str">
         <v>基础战斗</v>
       </c>
-      <c r="E9" s="6" t="str">
+      <c r="E9" s="11" t="str">
         <v>不同于攻击伤害</v>
       </c>
-      <c r="F9" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G9" s="6" t="str">
+      <c r="F9" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G9" s="11" t="str">
         <v>{"amount":2,"canKill":false}</v>
       </c>
-      <c r="H9" s="6" t="str">
+      <c r="H9" s="11" t="str">
         <v>[{"key":"amount","label":"失去生命","kind":"expr","options":null},{"key":"canKill","label":"可以使玩家死亡","kind":"bool","options":null}]</v>
       </c>
-      <c r="I9" s="6" t="str"/>
-      <c r="J9" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" ht="90" customHeight="1">
-      <c r="A10" s="11" t="n">
+      <c r="I9" s="10" t="str"/>
+      <c r="J9" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="9" t="n">
         <v>210005</v>
       </c>
-      <c r="B10" s="6" t="str">
+      <c r="B10" s="10" t="str">
         <v>KILL_IF</v>
       </c>
-      <c r="C10" s="6" t="str">
+      <c r="C10" s="10" t="str">
         <v>满足条件直接击杀</v>
       </c>
-      <c r="D10" s="6" t="str">
+      <c r="D10" s="10" t="str">
         <v>基础战斗</v>
       </c>
-      <c r="E10" s="6" t="str">
+      <c r="E10" s="11" t="str">
         <v>例如血量阈值斩杀</v>
       </c>
-      <c r="F10" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G10" s="6" t="str">
+      <c r="F10" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G10" s="11" t="str">
         <v>{"threshold":30}</v>
       </c>
-      <c r="H10" s="6" t="str">
+      <c r="H10" s="11" t="str">
         <v>[{"key":"threshold","label":"目标当前生命上限","kind":"expr","options":null}]</v>
       </c>
-      <c r="I10" s="6" t="str"/>
-      <c r="J10" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" ht="90" customHeight="1">
-      <c r="A11" s="11" t="n">
+      <c r="I10" s="10" t="str"/>
+      <c r="J10" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="9" t="n">
         <v>210006</v>
       </c>
-      <c r="B11" s="6" t="str">
+      <c r="B11" s="10" t="str">
         <v>MULTIPLY_BLOCK</v>
       </c>
-      <c r="C11" s="6" t="str">
+      <c r="C11" s="10" t="str">
         <v>改变当前格挡</v>
       </c>
-      <c r="D11" s="6" t="str">
+      <c r="D11" s="10" t="str">
         <v>基础战斗</v>
       </c>
-      <c r="E11" s="6" t="str">
+      <c r="E11" s="11" t="str">
         <v>例如 Entrench 翻倍</v>
       </c>
-      <c r="F11" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G11" s="6" t="str">
+      <c r="F11" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G11" s="11" t="str">
         <v>{"factor":2}</v>
       </c>
-      <c r="H11" s="6" t="str">
+      <c r="H11" s="11" t="str">
         <v>[{"key":"factor","label":"倍率","kind":"expr","options":null}]</v>
       </c>
-      <c r="I11" s="6" t="str"/>
-      <c r="J11" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K11" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" ht="90" customHeight="1">
-      <c r="A12" s="11" t="n">
+      <c r="I11" s="10" t="str"/>
+      <c r="J11" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="9" t="n">
         <v>210007</v>
       </c>
-      <c r="B12" s="6" t="str">
+      <c r="B12" s="10" t="str">
         <v>REMOVE_BLOCK</v>
       </c>
-      <c r="C12" s="6" t="str">
+      <c r="C12" s="10" t="str">
         <v>移除格挡</v>
       </c>
-      <c r="D12" s="6" t="str">
+      <c r="D12" s="10" t="str">
         <v>基础战斗</v>
       </c>
-      <c r="E12" s="6" t="str">
+      <c r="E12" s="11" t="str">
         <v>消除目标所有或部分格挡</v>
       </c>
-      <c r="F12" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G12" s="6" t="str">
+      <c r="F12" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G12" s="11" t="str">
         <v>{"amount":"ALL"}</v>
       </c>
-      <c r="H12" s="6" t="str">
+      <c r="H12" s="11" t="str">
         <v>[{"key":"amount","label":"数量 / ALL","kind":"expr","options":null}]</v>
       </c>
-      <c r="I12" s="6" t="str"/>
-      <c r="J12" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K12" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" ht="90" customHeight="1">
-      <c r="A13" s="11" t="n">
+      <c r="I12" s="10" t="str"/>
+      <c r="J12" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="9" t="n">
         <v>210008</v>
       </c>
-      <c r="B13" s="6" t="str">
+      <c r="B13" s="10" t="str">
         <v>PIERCE_BLOCK</v>
       </c>
-      <c r="C13" s="6" t="str">
+      <c r="C13" s="10" t="str">
         <v>融化 / 消去格挡</v>
       </c>
-      <c r="D13" s="6" t="str">
+      <c r="D13" s="10" t="str">
         <v>基础战斗</v>
       </c>
-      <c r="E13" s="6" t="str">
+      <c r="E13" s="11" t="str">
         <v>直接消除敌人格挡后执行其他效果</v>
       </c>
-      <c r="F13" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G13" s="6" t="str">
+      <c r="F13" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G13" s="11" t="str">
         <v>{"amount":"ALL"}</v>
       </c>
-      <c r="H13" s="6" t="str">
+      <c r="H13" s="11" t="str">
         <v>[{"key":"amount","label":"数量 / ALL","kind":"expr","options":null}]</v>
       </c>
-      <c r="I13" s="6" t="str"/>
-      <c r="J13" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K13" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="11" t="n">
+      <c r="I13" s="10" t="str"/>
+      <c r="J13" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="9" t="n">
         <v>210009</v>
       </c>
-      <c r="B14" s="6" t="str">
+      <c r="B14" s="10" t="str">
         <v>BLOCK_NEXT_TURN</v>
       </c>
-      <c r="C14" s="6" t="str">
+      <c r="C14" s="10" t="str">
         <v>下回合格挡</v>
       </c>
-      <c r="D14" s="6" t="str">
+      <c r="D14" s="10" t="str">
         <v>基础战斗</v>
       </c>
-      <c r="E14" s="6" t="str">
+      <c r="E14" s="11" t="str">
         <v>延迟获得格挡</v>
       </c>
-      <c r="F14" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G14" s="6" t="str">
+      <c r="F14" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G14" s="11" t="str">
         <v>{"amount":4}</v>
       </c>
-      <c r="H14" s="6" t="str">
+      <c r="H14" s="11" t="str">
         <v>[{"key":"amount","label":"格挡值","kind":"expr","options":null}]</v>
       </c>
-      <c r="I14" s="6" t="str"/>
-      <c r="J14" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K14" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="11" t="n">
+      <c r="I14" s="10" t="str"/>
+      <c r="J14" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="53.5" customHeight="1">
+      <c r="A15" s="9" t="n">
         <v>210010</v>
       </c>
-      <c r="B15" s="6" t="str">
+      <c r="B15" s="10" t="str">
         <v>APPLY_STATUS</v>
       </c>
-      <c r="C15" s="6" t="str">
+      <c r="C15" s="10" t="str">
         <v>施加增益 / 减益</v>
       </c>
-      <c r="D15" s="6" t="str">
+      <c r="D15" s="10" t="str">
         <v>状态与能力</v>
       </c>
-      <c r="E15" s="6" t="str">
+      <c r="E15" s="11" t="str">
         <v>力量、敏捷、虚弱、中毒、易伤、人工制品等</v>
       </c>
-      <c r="F15" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G15" s="6" t="str">
+      <c r="F15" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G15" s="11" t="str">
         <v>{"status":200003,"stacks":2,"duration":"DEFAULT"}</v>
       </c>
-      <c r="H15" s="6" t="str">
+      <c r="H15" s="11" t="str">
         <v>[{"key":"status","label":"状态 ID","kind":"enum","options":[]},{"key":"stacks","label":"层数","kind":"expr","options":null},{"key":"duration","label":"持续时间","kind":"enum","options":["DEFAULT","TURN","NEXT_TURN","COMBAT","RUN"]}]</v>
       </c>
-      <c r="I15" s="6" t="str"/>
-      <c r="J15" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K15" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="11" t="n">
+      <c r="I15" s="10" t="str"/>
+      <c r="J15" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="37.0" customHeight="1">
+      <c r="A16" s="9" t="n">
         <v>210011</v>
       </c>
-      <c r="B16" s="6" t="str">
+      <c r="B16" s="10" t="str">
         <v>REMOVE_STATUS</v>
       </c>
-      <c r="C16" s="6" t="str">
+      <c r="C16" s="10" t="str">
         <v>移除状态</v>
       </c>
-      <c r="D16" s="6" t="str">
+      <c r="D16" s="10" t="str">
         <v>状态与能力</v>
       </c>
-      <c r="E16" s="6" t="str">
+      <c r="E16" s="11" t="str">
         <v>可移除全部或部分层数</v>
       </c>
-      <c r="F16" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G16" s="6" t="str">
+      <c r="F16" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G16" s="11" t="str">
         <v>{"status":200003,"stacks":"ALL"}</v>
       </c>
-      <c r="H16" s="6" t="str">
+      <c r="H16" s="11" t="str">
         <v>[{"key":"status","label":"状态 ID / ALL","kind":"enum","options":[]},{"key":"stacks","label":"移除层数 / ALL","kind":"expr","options":null}]</v>
       </c>
-      <c r="I16" s="6" t="str"/>
-      <c r="J16" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K16" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" ht="90" customHeight="1">
-      <c r="A17" s="11" t="n">
+      <c r="I16" s="10" t="str"/>
+      <c r="J16" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" ht="37.0" customHeight="1">
+      <c r="A17" s="9" t="n">
         <v>210012</v>
       </c>
-      <c r="B17" s="6" t="str">
+      <c r="B17" s="10" t="str">
         <v>MULTIPLY_STATUS</v>
       </c>
-      <c r="C17" s="6" t="str">
+      <c r="C17" s="10" t="str">
         <v>按倍率修改状态层数</v>
       </c>
-      <c r="D17" s="6" t="str">
+      <c r="D17" s="10" t="str">
         <v>状态与能力</v>
       </c>
-      <c r="E17" s="6" t="str">
+      <c r="E17" s="11" t="str">
         <v>例如 Catalyst 将中毒翻倍</v>
       </c>
-      <c r="F17" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G17" s="6" t="str">
+      <c r="F17" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G17" s="11" t="str">
         <v>{"status":200003,"factor":2}</v>
       </c>
-      <c r="H17" s="6" t="str">
+      <c r="H17" s="11" t="str">
         <v>[{"key":"status","label":"状态 ID","kind":"enum","options":[]},{"key":"factor","label":"倍率","kind":"expr","options":null}]</v>
       </c>
-      <c r="I17" s="6" t="str"/>
-      <c r="J17" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K17" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" ht="90" customHeight="1">
-      <c r="A18" s="11" t="n">
+      <c r="I17" s="10" t="str"/>
+      <c r="J17" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" ht="53.5" customHeight="1">
+      <c r="A18" s="9" t="n">
         <v>210013</v>
       </c>
-      <c r="B18" s="6" t="str">
+      <c r="B18" s="10" t="str">
         <v>TRANSFER_STATUS</v>
       </c>
-      <c r="C18" s="6" t="str">
+      <c r="C18" s="10" t="str">
         <v>转移状态</v>
       </c>
-      <c r="D18" s="6" t="str">
+      <c r="D18" s="10" t="str">
         <v>状态与能力</v>
       </c>
-      <c r="E18" s="6" t="str">
+      <c r="E18" s="11" t="str">
         <v>在自己与敌人之间转移状态</v>
       </c>
-      <c r="F18" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G18" s="6" t="str">
+      <c r="F18" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G18" s="11" t="str">
         <v>{"status":200003,"amount":"ALL","destination":"ENEMY"}</v>
       </c>
-      <c r="H18" s="6" t="str">
+      <c r="H18" s="11" t="str">
         <v>[{"key":"status","label":"状态 ID","kind":"enum","options":[]},{"key":"amount","label":"转移层数 / ALL","kind":"expr","options":null},{"key":"destination","label":"目标","kind":"enum","options":["SELF","ENEMY"]}]</v>
       </c>
-      <c r="I18" s="6" t="str"/>
-      <c r="J18" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K18" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" ht="90" customHeight="1">
-      <c r="A19" s="11" t="n">
+      <c r="I18" s="10" t="str"/>
+      <c r="J18" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="9" t="n">
         <v>210014</v>
       </c>
-      <c r="B19" s="6" t="str">
+      <c r="B19" s="10" t="str">
         <v>CLEANSE</v>
       </c>
-      <c r="C19" s="6" t="str">
+      <c r="C19" s="10" t="str">
         <v>清除不利状态</v>
       </c>
-      <c r="D19" s="6" t="str">
+      <c r="D19" s="10" t="str">
         <v>状态与能力</v>
       </c>
-      <c r="E19" s="6" t="str">
+      <c r="E19" s="11" t="str">
         <v>按规则清除减益</v>
       </c>
-      <c r="F19" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G19" s="6" t="str">
+      <c r="F19" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G19" s="11" t="str">
         <v>{"filter":{"kind":"DEBUFF"}}</v>
       </c>
-      <c r="H19" s="6" t="str">
+      <c r="H19" s="11" t="str">
         <v>[{"key":"filter","label":"状态筛选 JSON","kind":"json","options":null}]</v>
       </c>
-      <c r="I19" s="6" t="str"/>
-      <c r="J19" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K19" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" ht="90" customHeight="1">
-      <c r="A20" s="11" t="n">
+      <c r="I19" s="10" t="str"/>
+      <c r="J19" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" ht="53.5" customHeight="1">
+      <c r="A20" s="9" t="n">
         <v>210015</v>
       </c>
-      <c r="B20" s="6" t="str">
+      <c r="B20" s="10" t="str">
         <v>MODIFY_STAT</v>
       </c>
-      <c r="C20" s="6" t="str">
+      <c r="C20" s="10" t="str">
         <v>改变基础数值</v>
       </c>
-      <c r="D20" s="6" t="str">
+      <c r="D20" s="10" t="str">
         <v>资源与数值</v>
       </c>
-      <c r="E20" s="6" t="str">
+      <c r="E20" s="11" t="str">
         <v>力量、敏捷等，支持持续时间</v>
       </c>
-      <c r="F20" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G20" s="6" t="str">
+      <c r="F20" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G20" s="11" t="str">
         <v>{"stat":200001,"amount":2,"duration":"COMBAT"}</v>
       </c>
-      <c r="H20" s="6" t="str">
+      <c r="H20" s="11" t="str">
         <v>[{"key":"stat","label":"属性","kind":"enum","options":[]},{"key":"amount","label":"变化量","kind":"expr","options":null},{"key":"duration","label":"有效期","kind":"enum","options":["ACTION","TURN","NEXT_TURN","COMBAT","RUN"]}]</v>
       </c>
-      <c r="I20" s="6" t="str"/>
-      <c r="J20" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K20" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" ht="90" customHeight="1">
-      <c r="A21" s="11" t="n">
+      <c r="I20" s="10" t="str"/>
+      <c r="J20" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" ht="37.0" customHeight="1">
+      <c r="A21" s="9" t="n">
         <v>210016</v>
       </c>
-      <c r="B21" s="6" t="str">
+      <c r="B21" s="10" t="str">
         <v>SET_STAT</v>
       </c>
-      <c r="C21" s="6" t="str">
+      <c r="C21" s="10" t="str">
         <v>设置属性</v>
       </c>
-      <c r="D21" s="6" t="str">
+      <c r="D21" s="10" t="str">
         <v>资源与数值</v>
       </c>
-      <c r="E21" s="6" t="str">
+      <c r="E21" s="11" t="str">
         <v>属性直接修改为指定值</v>
       </c>
-      <c r="F21" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G21" s="6" t="str">
+      <c r="F21" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G21" s="11" t="str">
         <v>{"stat":200001,"value":0}</v>
       </c>
-      <c r="H21" s="6" t="str">
+      <c r="H21" s="11" t="str">
         <v>[{"key":"stat","label":"属性","kind":"enum","options":[]},{"key":"value","label":"目标值","kind":"expr","options":null}]</v>
       </c>
-      <c r="I21" s="6" t="str"/>
-      <c r="J21" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K21" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" ht="90" customHeight="1">
-      <c r="A22" s="11" t="n">
+      <c r="I21" s="10" t="str"/>
+      <c r="J21" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="9" t="n">
         <v>210017</v>
       </c>
-      <c r="B22" s="6" t="str">
+      <c r="B22" s="10" t="str">
         <v>DOUBLE_STAT</v>
       </c>
-      <c r="C22" s="6" t="str">
+      <c r="C22" s="10" t="str">
         <v>属性翻倍</v>
       </c>
-      <c r="D22" s="6" t="str">
+      <c r="D22" s="10" t="str">
         <v>资源与数值</v>
       </c>
-      <c r="E22" s="6" t="str">
+      <c r="E22" s="11" t="str">
         <v>例如 Limit Break</v>
       </c>
-      <c r="F22" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G22" s="6" t="str">
+      <c r="F22" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G22" s="11" t="str">
         <v>{"stat":200001}</v>
       </c>
-      <c r="H22" s="6" t="str">
+      <c r="H22" s="11" t="str">
         <v>[{"key":"stat","label":"属性","kind":"enum","options":[]}]</v>
       </c>
-      <c r="I22" s="6" t="str"/>
-      <c r="J22" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K22" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" ht="90" customHeight="1">
-      <c r="A23" s="11" t="n">
+      <c r="I22" s="10" t="str"/>
+      <c r="J22" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="9" t="n">
         <v>210018</v>
       </c>
-      <c r="B23" s="6" t="str">
+      <c r="B23" s="10" t="str">
         <v>SET_INTANGIBLE</v>
       </c>
-      <c r="C23" s="6" t="str">
+      <c r="C23" s="10" t="str">
         <v>无实体</v>
       </c>
-      <c r="D23" s="6" t="str">
+      <c r="D23" s="10" t="str">
         <v>状态与能力</v>
       </c>
-      <c r="E23" s="6" t="str">
+      <c r="E23" s="11" t="str">
         <v>减少战斗伤害的能力</v>
       </c>
-      <c r="F23" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G23" s="6" t="str">
+      <c r="F23" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G23" s="11" t="str">
         <v>{"stacks":1}</v>
       </c>
-      <c r="H23" s="6" t="str">
+      <c r="H23" s="11" t="str">
         <v>[{"key":"stacks","label":"层数","kind":"expr","options":null}]</v>
       </c>
-      <c r="I23" s="6" t="str"/>
-      <c r="J23" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K23" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" ht="90" customHeight="1">
-      <c r="A24" s="11" t="n">
+      <c r="I23" s="10" t="str"/>
+      <c r="J23" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="9" t="n">
         <v>210019</v>
       </c>
-      <c r="B24" s="6" t="str">
+      <c r="B24" s="10" t="str">
         <v>IF</v>
       </c>
-      <c r="C24" s="6" t="str">
+      <c r="C24" s="10" t="str">
         <v>条件分支</v>
       </c>
-      <c r="D24" s="6" t="str">
+      <c r="D24" s="10" t="str">
         <v>流程与触发</v>
       </c>
-      <c r="E24" s="6" t="str">
+      <c r="E24" s="11" t="str">
         <v>满足条件走 THEN，不满足走 ELSE</v>
       </c>
-      <c r="F24" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G24" s="6" t="str">
+      <c r="F24" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G24" s="11" t="str">
         <v>{}</v>
       </c>
-      <c r="H24" s="6" t="str">
+      <c r="H24" s="11" t="str">
         <v>[]</v>
       </c>
-      <c r="I24" s="6" t="str">
+      <c r="I24" s="10" t="str">
         <v>if</v>
       </c>
-      <c r="J24" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K24" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" ht="90" customHeight="1">
-      <c r="A25" s="11" t="n">
+      <c r="J24" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="9" t="n">
         <v>210020</v>
       </c>
-      <c r="B25" s="6" t="str">
+      <c r="B25" s="10" t="str">
         <v>SEQUENCE</v>
       </c>
-      <c r="C25" s="6" t="str">
+      <c r="C25" s="10" t="str">
         <v>效果组 / 顺序执行</v>
       </c>
-      <c r="D25" s="6" t="str">
+      <c r="D25" s="10" t="str">
         <v>流程与触发</v>
       </c>
-      <c r="E25" s="6" t="str">
+      <c r="E25" s="11" t="str">
         <v>把多效果打包成一个步骤</v>
       </c>
-      <c r="F25" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G25" s="6" t="str">
+      <c r="F25" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G25" s="11" t="str">
         <v>{}</v>
       </c>
-      <c r="H25" s="6" t="str">
+      <c r="H25" s="11" t="str">
         <v>[]</v>
       </c>
-      <c r="I25" s="6" t="str">
+      <c r="I25" s="10" t="str">
         <v>children</v>
       </c>
-      <c r="J25" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K25" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" ht="90" customHeight="1">
-      <c r="A26" s="11" t="n">
+      <c r="J25" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" ht="37.0" customHeight="1">
+      <c r="A26" s="9" t="n">
         <v>210021</v>
       </c>
-      <c r="B26" s="6" t="str">
+      <c r="B26" s="10" t="str">
         <v>REPEAT</v>
       </c>
-      <c r="C26" s="6" t="str">
+      <c r="C26" s="10" t="str">
         <v>循环执行</v>
       </c>
-      <c r="D26" s="6" t="str">
+      <c r="D26" s="10" t="str">
         <v>流程与触发</v>
       </c>
-      <c r="E26" s="6" t="str">
+      <c r="E26" s="11" t="str">
         <v>固定或动态次数的多段效果</v>
       </c>
-      <c r="F26" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G26" s="6" t="str">
+      <c r="F26" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G26" s="11" t="str">
         <v>{"count":2,"maxIterations":30}</v>
       </c>
-      <c r="H26" s="6" t="str">
+      <c r="H26" s="11" t="str">
         <v>[{"key":"count","label":"重复次数","kind":"expr","options":null},{"key":"maxIterations","label":"安全上限","kind":"number","options":null}]</v>
       </c>
-      <c r="I26" s="6" t="str">
+      <c r="I26" s="10" t="str">
         <v>children</v>
       </c>
-      <c r="J26" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K26" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" ht="90" customHeight="1">
-      <c r="A27" s="11" t="n">
+      <c r="J26" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K26" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" ht="136.0" customHeight="1">
+      <c r="A27" s="9" t="n">
         <v>210022</v>
       </c>
-      <c r="B27" s="6" t="str">
+      <c r="B27" s="10" t="str">
         <v>REGISTER_TRIGGER</v>
       </c>
-      <c r="C27" s="6" t="str">
+      <c r="C27" s="10" t="str">
         <v>注册能力 / 持续触发</v>
       </c>
-      <c r="D27" s="6" t="str">
+      <c r="D27" s="10" t="str">
         <v>流程与触发</v>
       </c>
-      <c r="E27" s="6" t="str">
+      <c r="E27" s="11" t="str">
         <v>配置事件、监听过滤器、次数和持续范围</v>
       </c>
-      <c r="F27" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G27" s="6" t="str">
+      <c r="F27" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G27" s="11" t="str">
         <v>{"event":"ON_TURN_START","scope":"COMBAT","limit":0,"filter":{}}</v>
       </c>
-      <c r="H27" s="6" t="str">
+      <c r="H27" s="11" t="str">
         <v>[{"key":"event","label":"触发事件","kind":"enum","options":["ON_COMBAT_START","ON_TURN_START","ON_TURN_END","ON_CARD_DRAWN","ON_CARD_PLAYED","ON_ATTACK_PLAYED","ON_SKILL_PLAYED","ON_POWER_PLAYED","ON_DISCARD","ON_EXHAUST","ON_SHUFFLE","ON_DAMAGE_DEALT","ON_DAMAGE_TAKEN","ON_HP_LOSS","ON_ENEMY_DIED","ON_CARD_CREATED","ON_COMBAT_END"]},{"key":"scope","label":"有效期","kind":"enum","options":["TURN","NEXT_TURN","COMBAT","RUN"]},{"key":"limit","label":"最多触发次数（0=不限）","kind":"number","options":null},{"key":"filter","label":"事件过滤 JSON","kind":"json","options":null}]</v>
       </c>
-      <c r="I27" s="6" t="str">
+      <c r="I27" s="10" t="str">
         <v>children</v>
       </c>
-      <c r="J27" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K27" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" ht="90" customHeight="1">
-      <c r="A28" s="11" t="n">
+      <c r="J27" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K27" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" ht="70.0" customHeight="1">
+      <c r="A28" s="9" t="n">
         <v>210023</v>
       </c>
-      <c r="B28" s="6" t="str">
+      <c r="B28" s="10" t="str">
         <v>SCHEDULE</v>
       </c>
-      <c r="C28" s="6" t="str">
+      <c r="C28" s="10" t="str">
         <v>延迟执行</v>
       </c>
-      <c r="D28" s="6" t="str">
+      <c r="D28" s="10" t="str">
         <v>流程与触发</v>
       </c>
-      <c r="E28" s="6" t="str">
+      <c r="E28" s="11" t="str">
         <v>下回合或在指定时机执行；可快照选定卡</v>
       </c>
-      <c r="F28" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G28" s="6" t="str">
+      <c r="F28" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G28" s="11" t="str">
         <v>{"when":"NEXT_TURN_START","times":1,"capture":{}}</v>
       </c>
-      <c r="H28" s="6" t="str">
+      <c r="H28" s="11" t="str">
         <v>[{"key":"when","label":"执行时机","kind":"enum","options":["NEXT_TURN_START","NEXT_TURN_END","TURN_END","COMBAT_END","AFTER_ENEMY_TURN"]},{"key":"times","label":"执行次数","kind":"expr","options":null},{"key":"capture","label":"执行上下文快照 JSON","kind":"json","options":null}]</v>
       </c>
-      <c r="I28" s="6" t="str">
+      <c r="I28" s="10" t="str">
         <v>children</v>
       </c>
-      <c r="J28" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K28" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" ht="90" customHeight="1">
-      <c r="A29" s="11" t="n">
+      <c r="J28" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K28" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" ht="37.0" customHeight="1">
+      <c r="A29" s="9" t="n">
         <v>210024</v>
       </c>
-      <c r="B29" s="6" t="str">
+      <c r="B29" s="10" t="str">
         <v>CHOOSE_ONE</v>
       </c>
-      <c r="C29" s="6" t="str">
+      <c r="C29" s="10" t="str">
         <v>让玩家选择一项</v>
       </c>
-      <c r="D29" s="6" t="str">
+      <c r="D29" s="10" t="str">
         <v>流程与触发</v>
       </c>
-      <c r="E29" s="6" t="str">
+      <c r="E29" s="11" t="str">
         <v>每个直接子节点代表一个可选效果；多个效果可用 SEQUENCE</v>
       </c>
-      <c r="F29" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G29" s="6" t="str">
+      <c r="F29" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G29" s="11" t="str">
         <v>{"maxChoices":1,"showCount":3}</v>
       </c>
-      <c r="H29" s="6" t="str">
+      <c r="H29" s="11" t="str">
         <v>[{"key":"maxChoices","label":"选择数量","kind":"expr","options":null},{"key":"showCount","label":"展示选项数量","kind":"expr","options":null}]</v>
       </c>
-      <c r="I29" s="6" t="str">
+      <c r="I29" s="10" t="str">
         <v>children</v>
       </c>
-      <c r="J29" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K29" s="7" t="b">
+      <c r="J29" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K29" s="10" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="30" ht="90" customHeight="1">
-      <c r="A30" s="11" t="n">
+    <row r="30" ht="37.0" customHeight="1">
+      <c r="A30" s="9" t="n">
         <v>210025</v>
       </c>
-      <c r="B30" s="6" t="str">
+      <c r="B30" s="10" t="str">
         <v>RANDOM_CHOICE</v>
       </c>
-      <c r="C30" s="6" t="str">
+      <c r="C30" s="10" t="str">
         <v>从子效果中随机选取</v>
       </c>
-      <c r="D30" s="6" t="str">
+      <c r="D30" s="10" t="str">
         <v>流程与触发</v>
       </c>
-      <c r="E30" s="6" t="str">
+      <c r="E30" s="11" t="str">
         <v>按数量从选项中选择，不重复可配置</v>
       </c>
-      <c r="F30" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G30" s="6" t="str">
+      <c r="F30" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G30" s="11" t="str">
         <v>{"count":1,"unique":true}</v>
       </c>
-      <c r="H30" s="6" t="str">
+      <c r="H30" s="11" t="str">
         <v>[{"key":"count","label":"选择数量","kind":"expr","options":null},{"key":"unique","label":"不重复","kind":"bool","options":null}]</v>
       </c>
-      <c r="I30" s="6" t="str">
+      <c r="I30" s="10" t="str">
         <v>children</v>
       </c>
-      <c r="J30" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K30" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" ht="90" customHeight="1">
-      <c r="A31" s="11" t="n">
+      <c r="J30" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K30" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" ht="53.5" customHeight="1">
+      <c r="A31" s="9" t="n">
         <v>210026</v>
       </c>
-      <c r="B31" s="6" t="str">
+      <c r="B31" s="10" t="str">
         <v>DISCARD</v>
       </c>
-      <c r="C31" s="6" t="str">
+      <c r="C31" s="10" t="str">
         <v>弃牌</v>
       </c>
-      <c r="D31" s="6" t="str">
+      <c r="D31" s="10" t="str">
         <v>卡牌与牌堆</v>
       </c>
-      <c r="E31" s="6" t="str">
+      <c r="E31" s="11" t="str">
         <v>可由玩家选牌或随机</v>
       </c>
-      <c r="F31" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G31" s="6" t="str">
+      <c r="F31" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G31" s="11" t="str">
         <v>{"count":1,"mode":"SELECT","filter":{}}</v>
       </c>
-      <c r="H31" s="6" t="str">
+      <c r="H31" s="11" t="str">
         <v>[{"key":"count","label":"数量 / ALL","kind":"expr","options":null},{"key":"mode","label":"选择方式","kind":"enum","options":["SELECT","RANDOM","ALL","FILTER"]},{"key":"filter","label":"筛选 JSON","kind":"json","options":null}]</v>
       </c>
-      <c r="I31" s="6" t="str"/>
-      <c r="J31" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K31" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" ht="90" customHeight="1">
-      <c r="A32" s="11" t="n">
+      <c r="I31" s="10" t="str"/>
+      <c r="J31" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K31" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" ht="70.0" customHeight="1">
+      <c r="A32" s="9" t="n">
         <v>210027</v>
       </c>
-      <c r="B32" s="6" t="str">
+      <c r="B32" s="10" t="str">
         <v>EXHAUST</v>
       </c>
-      <c r="C32" s="6" t="str">
+      <c r="C32" s="10" t="str">
         <v>消耗卡牌</v>
       </c>
-      <c r="D32" s="6" t="str">
+      <c r="D32" s="10" t="str">
         <v>卡牌与牌堆</v>
       </c>
-      <c r="E32" s="6" t="str">
+      <c r="E32" s="11" t="str">
         <v>可指定手牌 / 抽牌堆等</v>
       </c>
-      <c r="F32" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G32" s="6" t="str">
+      <c r="F32" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G32" s="11" t="str">
         <v>{"count":1,"zone":"HAND","mode":"SELECT","filter":{}}</v>
       </c>
-      <c r="H32" s="6" t="str">
+      <c r="H32" s="11" t="str">
         <v>[{"key":"count","label":"数量 / ALL","kind":"expr","options":null},{"key":"zone","label":"来源牌堆","kind":"enum","options":["HAND","DRAW","DISCARD","EXHAUST","ANY"]},{"key":"mode","label":"选择方式","kind":"enum","options":["SELECT","RANDOM","ALL","FILTER"]},{"key":"filter","label":"筛选 JSON","kind":"json","options":null}]</v>
       </c>
-      <c r="I32" s="6" t="str"/>
-      <c r="J32" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K32" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" ht="90" customHeight="1">
-      <c r="A33" s="11" t="n">
+      <c r="I32" s="10" t="str"/>
+      <c r="J32" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K32" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="9" t="n">
         <v>210028</v>
       </c>
-      <c r="B33" s="6" t="str">
+      <c r="B33" s="10" t="str">
         <v>DISCARD_HAND</v>
       </c>
-      <c r="C33" s="6" t="str">
+      <c r="C33" s="10" t="str">
         <v>弃掉整手牌</v>
       </c>
-      <c r="D33" s="6" t="str">
+      <c r="D33" s="10" t="str">
         <v>卡牌与牌堆</v>
       </c>
-      <c r="E33" s="6" t="str">
+      <c r="E33" s="11" t="str">
         <v>弃掉满足筛选条件的全部手牌</v>
       </c>
-      <c r="F33" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G33" s="6" t="str">
+      <c r="F33" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G33" s="11" t="str">
         <v>{"filter":{}}</v>
       </c>
-      <c r="H33" s="6" t="str">
+      <c r="H33" s="11" t="str">
         <v>[{"key":"filter","label":"筛选条件","kind":"json","options":null}]</v>
       </c>
-      <c r="I33" s="6" t="str"/>
-      <c r="J33" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K33" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" ht="90" customHeight="1">
-      <c r="A34" s="11" t="n">
+      <c r="I33" s="10" t="str"/>
+      <c r="J33" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K33" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="9" t="n">
         <v>210029</v>
       </c>
-      <c r="B34" s="6" t="str">
+      <c r="B34" s="10" t="str">
         <v>EXHAUST_HAND</v>
       </c>
-      <c r="C34" s="6" t="str">
+      <c r="C34" s="10" t="str">
         <v>消耗整手牌</v>
       </c>
-      <c r="D34" s="6" t="str">
+      <c r="D34" s="10" t="str">
         <v>卡牌与牌堆</v>
       </c>
-      <c r="E34" s="6" t="str">
+      <c r="E34" s="11" t="str">
         <v>消耗满足筛选条件的全部手牌</v>
       </c>
-      <c r="F34" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G34" s="6" t="str">
+      <c r="F34" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G34" s="11" t="str">
         <v>{"filter":{}}</v>
       </c>
-      <c r="H34" s="6" t="str">
+      <c r="H34" s="11" t="str">
         <v>[{"key":"filter","label":"筛选条件","kind":"json","options":null}]</v>
       </c>
-      <c r="I34" s="6" t="str"/>
-      <c r="J34" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K34" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" ht="90" customHeight="1">
-      <c r="A35" s="11" t="n">
+      <c r="I34" s="10" t="str"/>
+      <c r="J34" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K34" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="9" t="n">
         <v>210030</v>
       </c>
-      <c r="B35" s="6" t="str">
+      <c r="B35" s="10" t="str">
         <v>EXHAUST_THIS_CARD</v>
       </c>
-      <c r="C35" s="6" t="str">
+      <c r="C35" s="10" t="str">
         <v>消耗这张卡</v>
       </c>
-      <c r="D35" s="6" t="str">
+      <c r="D35" s="10" t="str">
         <v>卡牌与牌堆</v>
       </c>
-      <c r="E35" s="6" t="str">
+      <c r="E35" s="11" t="str">
         <v>例如虚无状态抽入手牌后立即消耗</v>
       </c>
-      <c r="F35" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G35" s="6" t="str">
+      <c r="F35" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G35" s="11" t="str">
         <v>{}</v>
       </c>
-      <c r="H35" s="6" t="str">
+      <c r="H35" s="11" t="str">
         <v>[]</v>
       </c>
-      <c r="I35" s="6" t="str"/>
-      <c r="J35" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K35" s="7" t="b">
+      <c r="I35" s="10" t="str"/>
+      <c r="J35" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K35" s="10" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="36" ht="90" customHeight="1">
-      <c r="A36" s="11" t="n">
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="9" t="n">
         <v>210031</v>
       </c>
-      <c r="B36" s="6" t="str">
+      <c r="B36" s="10" t="str">
         <v>GAIN_GOLD</v>
       </c>
-      <c r="C36" s="6" t="str">
+      <c r="C36" s="10" t="str">
         <v>获得金币</v>
       </c>
-      <c r="D36" s="6" t="str">
+      <c r="D36" s="10" t="str">
         <v>资源与数值</v>
       </c>
-      <c r="E36" s="6" t="str">
+      <c r="E36" s="11" t="str">
         <v>可由击杀触发</v>
       </c>
-      <c r="F36" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G36" s="6" t="str">
+      <c r="F36" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G36" s="11" t="str">
         <v>{"amount":20}</v>
       </c>
-      <c r="H36" s="6" t="str">
+      <c r="H36" s="11" t="str">
         <v>[{"key":"amount","label":"金币数量","kind":"expr","options":null}]</v>
       </c>
-      <c r="I36" s="6" t="str"/>
-      <c r="J36" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K36" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" ht="90" customHeight="1">
-      <c r="A37" s="11" t="n">
+      <c r="I36" s="10" t="str"/>
+      <c r="J36" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K36" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="9" t="n">
         <v>210032</v>
       </c>
-      <c r="B37" s="6" t="str">
+      <c r="B37" s="10" t="str">
         <v>LOSE_GOLD</v>
       </c>
-      <c r="C37" s="6" t="str">
+      <c r="C37" s="10" t="str">
         <v>失去金币</v>
       </c>
-      <c r="D37" s="6" t="str">
+      <c r="D37" s="10" t="str">
         <v>资源与数值</v>
       </c>
-      <c r="E37" s="6" t="str">
+      <c r="E37" s="11" t="str">
         <v>直接减少金币</v>
       </c>
-      <c r="F37" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G37" s="6" t="str">
+      <c r="F37" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G37" s="11" t="str">
         <v>{"amount":20}</v>
       </c>
-      <c r="H37" s="6" t="str">
+      <c r="H37" s="11" t="str">
         <v>[{"key":"amount","label":"金币数量","kind":"expr","options":null}]</v>
       </c>
-      <c r="I37" s="6" t="str"/>
-      <c r="J37" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K37" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" ht="90" customHeight="1">
-      <c r="A38" s="11" t="n">
+      <c r="I37" s="10" t="str"/>
+      <c r="J37" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K37" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" ht="53.5" customHeight="1">
+      <c r="A38" s="9" t="n">
         <v>210033</v>
       </c>
-      <c r="B38" s="6" t="str">
+      <c r="B38" s="10" t="str">
         <v>SET_VARIABLE</v>
       </c>
-      <c r="C38" s="6" t="str">
+      <c r="C38" s="10" t="str">
         <v>设置临时变量</v>
       </c>
-      <c r="D38" s="6" t="str">
+      <c r="D38" s="10" t="str">
         <v>流程与触发</v>
       </c>
-      <c r="E38" s="6" t="str">
+      <c r="E38" s="11" t="str">
         <v>例如记录本次伤害总量</v>
       </c>
-      <c r="F38" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G38" s="6" t="str">
+      <c r="F38" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G38" s="11" t="str">
         <v>{"name":"temp","value":0,"scope":"ACTION"}</v>
       </c>
-      <c r="H38" s="6" t="str">
+      <c r="H38" s="11" t="str">
         <v>[{"key":"name","label":"变量名","kind":"text","options":null},{"key":"value","label":"数值 / 表达式","kind":"expr","options":null},{"key":"scope","label":"作用域","kind":"enum","options":["ACTION","TURN","COMBAT"]}]</v>
       </c>
-      <c r="I38" s="6" t="str"/>
-      <c r="J38" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K38" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" ht="90" customHeight="1">
-      <c r="A39" s="11" t="n">
+      <c r="I38" s="10" t="str"/>
+      <c r="J38" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K38" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" ht="70.0" customHeight="1">
+      <c r="A39" s="9" t="n">
         <v>210034</v>
       </c>
-      <c r="B39" s="6" t="str">
+      <c r="B39" s="10" t="str">
         <v>MODIFY_VARIABLE</v>
       </c>
-      <c r="C39" s="6" t="str">
+      <c r="C39" s="10" t="str">
         <v>修改临时变量</v>
       </c>
-      <c r="D39" s="6" t="str">
+      <c r="D39" s="10" t="str">
         <v>流程与触发</v>
       </c>
-      <c r="E39" s="6" t="str">
+      <c r="E39" s="11" t="str">
         <v>变量加法或乘法</v>
       </c>
-      <c r="F39" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G39" s="6" t="str">
+      <c r="F39" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G39" s="11" t="str">
         <v>{"name":"temp","operator":"ADD","value":1,"scope":"ACTION"}</v>
       </c>
-      <c r="H39" s="6" t="str">
+      <c r="H39" s="11" t="str">
         <v>[{"key":"name","label":"变量名","kind":"text","options":null},{"key":"operator","label":"操作","kind":"enum","options":["ADD","MULTIPLY","SET","MIN","MAX"]},{"key":"value","label":"值 / 表达式","kind":"expr","options":null},{"key":"scope","label":"作用域","kind":"enum","options":["ACTION","TURN","COMBAT"]}]</v>
       </c>
-      <c r="I39" s="6" t="str"/>
-      <c r="J39" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K39" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" ht="90" customHeight="1">
-      <c r="A40" s="11" t="n">
+      <c r="I39" s="10" t="str"/>
+      <c r="J39" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K39" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" ht="53.5" customHeight="1">
+      <c r="A40" s="9" t="n">
         <v>210035</v>
       </c>
-      <c r="B40" s="6" t="str">
+      <c r="B40" s="10" t="str">
         <v>ADD_CARD</v>
       </c>
-      <c r="C40" s="6" t="str">
+      <c r="C40" s="10" t="str">
         <v>添加卡牌</v>
       </c>
-      <c r="D40" s="6" t="str">
+      <c r="D40" s="10" t="str">
         <v>卡牌与牌堆</v>
       </c>
-      <c r="E40" s="6" t="str">
+      <c r="E40" s="11" t="str">
         <v>将指定配置卡牌加入抽牌堆或弃牌堆</v>
       </c>
-      <c r="F40" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G40" s="6" t="str">
+      <c r="F40" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G40" s="11" t="str">
         <v>{"cardId":20001,"count":1,"pile":"DISCARD"}</v>
       </c>
-      <c r="H40" s="6" t="str">
+      <c r="H40" s="11" t="str">
         <v>[{"key":"cardId","label":"卡牌编号","kind":"number","options":null},{"key":"count","label":"数量","kind":"expr","options":null},{"key":"pile","label":"加入牌堆","kind":"enum","options":["DRAW","DISCARD"]}]</v>
       </c>
-      <c r="I40" s="6" t="str"/>
-      <c r="J40" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K40" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" ht="90" customHeight="1">
-      <c r="A41" s="11" t="n">
+      <c r="I40" s="10" t="str"/>
+      <c r="J40" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K40" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" ht="53.5" customHeight="1">
+      <c r="A41" s="9" t="n">
         <v>210036</v>
       </c>
-      <c r="B41" s="6" t="str">
+      <c r="B41" s="10" t="str">
         <v>MODIFY_CARD_VALUE</v>
       </c>
-      <c r="C41" s="6" t="str">
+      <c r="C41" s="10" t="str">
         <v>增加卡牌数值</v>
       </c>
-      <c r="D41" s="6" t="str">
+      <c r="D41" s="10" t="str">
         <v>资源与数值</v>
       </c>
-      <c r="E41" s="6" t="str">
+      <c r="E41" s="11" t="str">
         <v>增加攻击或格挡卡牌的结算数值</v>
       </c>
-      <c r="F41" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G41" s="6" t="str">
+      <c r="F41" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G41" s="11" t="str">
         <v>{"kind":"DAMAGE","amount":2,"timing":"COMBAT"}</v>
       </c>
-      <c r="H41" s="6" t="str">
+      <c r="H41" s="11" t="str">
         <v>[{"key":"kind","label":"数值类型","kind":"enum","options":["DAMAGE","BLOCK"]},{"key":"amount","label":"增加量","kind":"expr","options":null},{"key":"timing","label":"生效范围","kind":"enum","options":["COMBAT","NEXT_CARD"]}]</v>
       </c>
-      <c r="I41" s="6" t="str"/>
-      <c r="J41" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K41" s="7" t="b">
+      <c r="I41" s="10" t="str"/>
+      <c r="J41" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K41" s="10" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="42" ht="90" customHeight="1">
-      <c r="A42" s="11" t="n">
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="9" t="n">
         <v>210037</v>
       </c>
-      <c r="B42" s="6" t="str">
+      <c r="B42" s="10" t="str">
         <v>GAIN_ENERGY</v>
       </c>
-      <c r="C42" s="6" t="str">
+      <c r="C42" s="10" t="str">
         <v>获得能量</v>
       </c>
-      <c r="D42" s="6" t="str">
+      <c r="D42" s="10" t="str">
         <v>资源与数值</v>
       </c>
-      <c r="E42" s="6" t="str">
+      <c r="E42" s="11" t="str">
         <v>增减玩家能量并触发能量变化事件</v>
       </c>
-      <c r="F42" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G42" s="6" t="str">
+      <c r="F42" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G42" s="11" t="str">
         <v>{"amount":1}</v>
       </c>
-      <c r="H42" s="6" t="str">
+      <c r="H42" s="11" t="str">
         <v>[{"key":"amount","label":"能量变化量","kind":"expr","options":null}]</v>
       </c>
-      <c r="I42" s="6" t="str"/>
-      <c r="J42" s="7" t="b">
+      <c r="I42" s="10" t="str"/>
+      <c r="J42" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="K42" s="7" t="b">
+      <c r="K42" s="10" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="43" ht="90" customHeight="1">
-      <c r="A43" s="11" t="n">
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="9" t="n">
         <v>210038</v>
       </c>
-      <c r="B43" s="6" t="str">
+      <c r="B43" s="10" t="str">
         <v>DRAW</v>
       </c>
-      <c r="C43" s="6" t="str">
+      <c r="C43" s="10" t="str">
         <v>额外抽牌</v>
       </c>
-      <c r="D43" s="6" t="str">
+      <c r="D43" s="10" t="str">
         <v>卡牌与牌堆</v>
       </c>
-      <c r="E43" s="6" t="str">
+      <c r="E43" s="11" t="str">
         <v>抽取指定数量的卡牌</v>
       </c>
-      <c r="F43" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G43" s="6" t="str">
+      <c r="F43" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G43" s="11" t="str">
         <v>{"count":1}</v>
       </c>
-      <c r="H43" s="6" t="str">
+      <c r="H43" s="11" t="str">
         <v>[{"key":"count","label":"数量","kind":"expr","options":null}]</v>
       </c>
-      <c r="I43" s="6" t="str"/>
-      <c r="J43" s="7" t="b">
+      <c r="I43" s="10" t="str"/>
+      <c r="J43" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="K43" s="7" t="b">
+      <c r="K43" s="10" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="44" ht="90" customHeight="1">
-      <c r="A44" s="11" t="n">
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="9" t="n">
         <v>210039</v>
       </c>
-      <c r="B44" s="6" t="str">
+      <c r="B44" s="10" t="str">
         <v>RETAIN_BLOCK</v>
       </c>
-      <c r="C44" s="6" t="str">
+      <c r="C44" s="10" t="str">
         <v>保留格挡</v>
       </c>
-      <c r="D44" s="6" t="str">
+      <c r="D44" s="10" t="str">
         <v>基础战斗</v>
       </c>
-      <c r="E44" s="6" t="str">
+      <c r="E44" s="11" t="str">
         <v>增加玩家下一回合可以保留的格挡上限</v>
       </c>
-      <c r="F44" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G44" s="6" t="str">
+      <c r="F44" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G44" s="11" t="str">
         <v>{"amount":5}</v>
       </c>
-      <c r="H44" s="6" t="str">
+      <c r="H44" s="11" t="str">
         <v>[{"key":"amount","label":"保留上限增量","kind":"expr","options":null}]</v>
       </c>
-      <c r="I44" s="6" t="str"/>
-      <c r="J44" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K44" s="7" t="b">
+      <c r="I44" s="10" t="str"/>
+      <c r="J44" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K44" s="10" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="90" customHeight="1">
-      <c r="A45" s="11" t="n">
+    <row r="45" ht="37.0" customHeight="1">
+      <c r="A45" s="9" t="n">
         <v>210040</v>
       </c>
-      <c r="B45" s="6" t="str">
+      <c r="B45" s="10" t="str">
         <v>FREE_DICE</v>
       </c>
-      <c r="C45" s="6" t="str">
+      <c r="C45" s="10" t="str">
         <v>免骰出牌</v>
       </c>
-      <c r="D45" s="6" t="str">
+      <c r="D45" s="10" t="str">
         <v>卡牌与牌堆</v>
       </c>
-      <c r="E45" s="6" t="str">
+      <c r="E45" s="11" t="str">
         <v>授予玩家指定数量的免骰出牌次数</v>
       </c>
-      <c r="F45" s="6" t="str">
-        <v>SELF</v>
-      </c>
-      <c r="G45" s="6" t="str">
+      <c r="F45" s="10" t="str">
+        <v>SELF</v>
+      </c>
+      <c r="G45" s="11" t="str">
         <v>{"count":1,"scope":"TURN"}</v>
       </c>
-      <c r="H45" s="6" t="str">
+      <c r="H45" s="11" t="str">
         <v>[{"key":"count","label":"次数","kind":"expr","options":null},{"key":"scope","label":"持续范围","kind":"enum","options":["TURN","COMBAT"]}]</v>
       </c>
-      <c r="I45" s="6" t="str"/>
-      <c r="J45" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K45" s="7" t="b">
+      <c r="I45" s="10" t="str"/>
+      <c r="J45" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K45" s="10" t="b">
         <v>0</v>
       </c>
     </row>

--- a/策划/excel/21_BattleEffect.xlsx
+++ b/策划/excel/21_BattleEffect.xlsx
@@ -607,13 +607,13 @@
     <t>卡牌与资源规则</t>
   </si>
   <si>
-    <t>配置持续免骰、下一攻击免骰或重复、禁抽、禁回能、首次格挡翻倍、易伤增幅。</t>
-  </si>
-  <si>
-    <t>{"kind":"SKILL_FREE_EXHAUST","amount":1}</t>
-  </si>
-  <si>
-    <t>[{"key":"kind","label":"规则","kind":"enum","options":["SKILL_FREE_EXHAUST","NEXT_ATTACK_FREE","NEXT_ATTACK_REPEAT","LOCK_DRAW","LOCK_ENERGY","FIRST_BLOCK_DOUBLE","VULNERABLE_BONUS"]},{"key":"amount","label":"数量或增幅","kind":"expr","options":null}]</t>
+    <t>下一张攻击牌免骰或重复、禁抽、禁回能；持续规则配置在Buff表中。</t>
+  </si>
+  <si>
+    <t>{"kind":"NEXT_ATTACK_FREE","amount":1}</t>
+  </si>
+  <si>
+    <t>[{"key":"kind","label":"规则","kind":"enum","options":["LOCK_DRAW","LOCK_ENERGY","NEXT_ATTACK_FREE","NEXT_ATTACK_REPEAT"]},{"key":"amount","label":"数量或增幅","kind":"expr","options":null}]</t>
   </si>
 </sst>
 </file>
